--- a/Yuno_ICP_Bank.xlsx
+++ b/Yuno_ICP_Bank.xlsx
@@ -437,7 +437,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="92" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -470,7 +470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hotels</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eSIM</t>
+          <t>Telco &amp; Connectivity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>E-comm marketplace</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Music/audio</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mobility super-app</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Embedded insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AI / Dev</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Online travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Parking/mobility</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Digital insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mobile F2P/esports</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Food/q-commerce</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Super-app</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Food delivery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gym chain</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mobile F2P</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Food/q-commerce</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Food delivery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Classifieds</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Gym chain</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Crypto/investing</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Neobank</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>E-comm marketplace</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Embedded insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Event ticketing</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Fashion e-comm</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Music/audio</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>QSR</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mobile puzzle</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Flights OTA/sub</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Investing/crypto</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Car rental</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EV charging sub</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mobile F2P</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>B2B bedbank</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Meal-kit sub</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Food delivery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Music/audio</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Used-car marketplace</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Mobile F2P</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AAA/mobile</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MVNO</t>
+          <t>Telco &amp; Connectivity</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Social-commerce</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Hotels</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>AAA gacha</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Hotels</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cruise</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Mobile RPG/gacha</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>F2P MMORPG</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>E-comm marketplace</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Food/q-commerce</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Proptech</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>QSR</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Digital insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Car rental</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Creator</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Brokerage/neobank</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OTA/super-app</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Hybrid-casual</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Corporate wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mobile gaming</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>QSR</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Subscription beauty</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Subscription tech rental</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>eSIM</t>
+          <t>Telco &amp; Connectivity</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Pet insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Charity/crowdfunding</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MVNO</t>
+          <t>Telco &amp; Connectivity</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Dev</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Webtoon/comics</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Dev</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Audio/audiobooks</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Embedded insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Smart-energy sub</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>eSIM/MVNO</t>
+          <t>Telco &amp; Connectivity</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>iGaming</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Digital insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Airline group</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>EV charging</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>AAA/mobile</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>iGaming</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>iGaming</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>E-comm marketplace</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Music/audio</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Ride-hailing</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Mental health</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Super-app</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Retail e-comm</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Mobile strategy</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Fast-casual</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Mobile gacha</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Cruise</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Ride-hailing</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Micromobility</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Food/q-commerce</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Dev</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Super-app</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Investing/brokerage</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Mental health</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Airline group</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Ride-hailing</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>EV charging sub</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Food delivery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Hotels</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>E-comm super-app</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Creator</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Cinema chain</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>E-comm marketplace</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Creator</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Car rental</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Proptech</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Coffee chain</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Home e-comm</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Hotels</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DIY marketplace</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Neobank</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Neobank</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>MMORPG</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>E-comm/food</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Creator</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Remittance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>AAA/MMO</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Webtoon/comics</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Fintech super-app</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Mobile mid-core</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Mobile F2P</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Hotels</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Dev</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>AAA/mobile</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Hotels</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>AAA/mobile</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Coffee chain</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Audiobooks</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>QSR</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>iGaming</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>E-comm marketplace</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Brokerage</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Privacy SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Travel/cruise</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Neobank/investing</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>eSIM</t>
+          <t>Telco &amp; Connectivity</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Dev</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>C2C luxury resale</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>OTT/sports</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Game publisher</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Micromobility</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Food/retail delivery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Brokerage/crypto</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Food/q-commerce</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Music-game</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Crypto neobank</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Charity/crowdfunding</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Corporate cards</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Crypto wallet</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Fitness sub</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Charity/crowdfunding</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Mental health</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Q-commerce gifting</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Digital insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Casual publisher</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Edtech tutoring</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Meal-kit sub</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Hybrid-casual</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Embedded micro-insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Mental health</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Audio/audiobooks</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Crypto neobank</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Crypto/fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Meal-kit sub</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>DTC fashion</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Sports/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Luxury DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Event ticketing</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>EV charging</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>eSIM</t>
+          <t>Telco &amp; Connectivity</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Dev</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>VPN/SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Event ticketing</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>C2C marketplace</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Travel metasearch</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Charity/crowdfunding</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Real-money skill</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Freelance marketplace</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Crypto on-ramp</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Dating/social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>News/publishing</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Q-commerce</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Coffee chain</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Food delivery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Fintech lending</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Food delivery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>iGaming</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>News/publishing</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Mobile F2P</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>iGaming/iLottery</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Hotels</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Cruise</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Smart-energy sub</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>iGaming</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -13076,7 +13076,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>E-comm/ecosystem</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -13142,7 +13142,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>News/publishing</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Food delivery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>iGaming</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -13252,7 +13252,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Fintech BNPL</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>E-comm/q-commerce</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Mobility</t>
+          <t>Mobility &amp; Energy</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Brokerage</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Airline</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Streaming</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -13560,7 +13560,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Neobank</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Subscription beauty</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Food delivery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Tours &amp; activities</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Dating</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Mobile gacha</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>DTC beauty</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -14352,7 +14352,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>B2B food marketplace</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Healthtech</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -14528,7 +14528,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Hybrid-casual</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Creator</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Proptech</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -14616,7 +14616,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>F2P publisher</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Grocery sub</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Browser/mobile</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Fintech corp cards</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Online grocery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Insurtech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -14858,7 +14858,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Webtoon/comics</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Food delivery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Mobile mid-core</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Meal-kit sub</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Crypto exchange</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -15166,7 +15166,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Fintech wallet</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Digital insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Mobile F2P</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Podcast/audio</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Content/audio</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Coffee/food</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Fashion flash-sale</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Privacy SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Hyper-casual</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Investing/neobank</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Hotels</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Digital motor insurance</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -15562,7 +15562,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -15584,7 +15584,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>RMG</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -15650,7 +15650,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Health/Wellness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>SaaS</t>
+          <t>SaaS &amp; Software</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Mobile gaming</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>Webtoon/comics</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Music/audio</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Gaming/Ent</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>Health &amp; Wellness</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Home e-comm</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -15980,7 +15980,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Neobank</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Mobile casual</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -16024,7 +16024,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Q-commerce</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>OTT/video</t>
+          <t>Media &amp; Streaming</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>DTC</t>
+          <t>E-commerce &amp; Retail</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -16156,7 +16156,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Q-commerce</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Q-commerce</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -16222,7 +16222,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Resort/cruise</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>OTA</t>
+          <t>Travel &amp; Experiences</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -16288,7 +16288,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Edtech</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Online grocery</t>
+          <t>Food &amp; Delivery</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Creator/Social</t>
+          <t>Creator &amp; Social</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech &amp; Crypto</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Consumer AI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -16442,7 +16442,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">

--- a/Yuno_ICP_Bank.xlsx
+++ b/Yuno_ICP_Bank.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -13318,7 +13318,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -15914,7 +15914,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -16442,7 +16442,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">

--- a/Yuno_ICP_Bank.xlsx
+++ b/Yuno_ICP_Bank.xlsx
@@ -14629,7 +14629,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.lemon.me</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>[Argentina] On-ramp routing + card auth uplift</t>
